--- a/Fuerza_Especifica_Diego.xlsx
+++ b/Fuerza_Especifica_Diego.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_EA1E3DD4CEA9EAF2ADF31EA80A8406CD7C06700A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="66">
   <si>
     <t>Día</t>
   </si>
@@ -203,13 +217,22 @@
   </si>
   <si>
     <t>Core</t>
+  </si>
+  <si>
+    <t>Jalon lateral en polea</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/GNtFIPlsuDk?si=4w5A5-yOH6vZo-rR</t>
+  </si>
+  <si>
+    <t>Hombro</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,6 +254,14 @@
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -265,33 +296,44 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="3">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -329,7 +371,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -363,6 +405,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -397,9 +440,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -572,11 +616,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="18.0234375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -590,7 +637,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -604,7 +651,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -618,7 +665,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -632,7 +679,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -646,7 +693,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -660,7 +707,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -674,7 +721,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -688,7 +735,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -702,7 +749,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -716,7 +763,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -730,7 +777,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -744,7 +791,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -758,7 +805,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -772,7 +819,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -786,7 +833,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -800,7 +847,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -814,21 +861,21 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>34</v>
+        <v>63</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -842,7 +889,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -856,7 +903,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -870,7 +917,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -884,7 +931,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -898,7 +945,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -912,7 +959,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -926,7 +973,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -940,7 +987,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -954,7 +1001,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -968,7 +1015,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>7</v>
       </c>
@@ -982,7 +1029,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -996,7 +1043,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -1010,7 +1057,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -1024,7 +1071,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -1040,38 +1087,38 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1"/>
-    <hyperlink ref="C3" r:id="rId2"/>
-    <hyperlink ref="C4" r:id="rId3"/>
-    <hyperlink ref="C5" r:id="rId4"/>
-    <hyperlink ref="C6" r:id="rId5"/>
-    <hyperlink ref="C7" r:id="rId6"/>
-    <hyperlink ref="C8" r:id="rId7"/>
-    <hyperlink ref="C9" r:id="rId8"/>
-    <hyperlink ref="C10" r:id="rId9"/>
-    <hyperlink ref="C11" r:id="rId10"/>
-    <hyperlink ref="C12" r:id="rId11"/>
-    <hyperlink ref="C13" r:id="rId12"/>
-    <hyperlink ref="C14" r:id="rId13"/>
-    <hyperlink ref="C15" r:id="rId14"/>
-    <hyperlink ref="C16" r:id="rId15"/>
-    <hyperlink ref="C17" r:id="rId16"/>
-    <hyperlink ref="C18" r:id="rId17"/>
-    <hyperlink ref="C19" r:id="rId18"/>
-    <hyperlink ref="C20" r:id="rId19"/>
-    <hyperlink ref="C21" r:id="rId20"/>
-    <hyperlink ref="C22" r:id="rId21"/>
-    <hyperlink ref="C23" r:id="rId22"/>
-    <hyperlink ref="C24" r:id="rId23"/>
-    <hyperlink ref="C25" r:id="rId24"/>
-    <hyperlink ref="C26" r:id="rId25"/>
-    <hyperlink ref="C27" r:id="rId26"/>
-    <hyperlink ref="C28" r:id="rId27"/>
-    <hyperlink ref="C29" r:id="rId28"/>
-    <hyperlink ref="C30" r:id="rId29"/>
-    <hyperlink ref="C31" r:id="rId30"/>
-    <hyperlink ref="C32" r:id="rId31"/>
-    <hyperlink ref="C33" r:id="rId32"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="C12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="C13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="C14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="C15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="C16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="C17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="C18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="C19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="C20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="C21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="C22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="C23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="C24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="C25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="C26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="C27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="C28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="C29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="C30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="C31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="C32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="C33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
